--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_o_higgins.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:51</t>
+    <t xml:space="preserve">2026-09-24 00:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -555,13 +555,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.69</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>-0.11</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="4">
@@ -601,13 +601,13 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.72</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="5">
@@ -624,13 +624,13 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.57</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>-0.05</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="6">
@@ -647,13 +647,13 @@
         <v>10</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.5</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>-0.04</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="7">
@@ -670,13 +670,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="8">
@@ -693,13 +693,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="9">
@@ -716,13 +716,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="10">
@@ -739,13 +739,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.24</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="11">
@@ -762,13 +762,13 @@
         <v>16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.22</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="12">
@@ -785,13 +785,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="2" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>-0.32</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>-0.35</v>
       </c>
     </row>
     <row r="13">
@@ -811,10 +811,10 @@
         <v>-0.03</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="14">
@@ -831,13 +831,13 @@
         <v>16</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.39</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="15">
@@ -854,13 +854,13 @@
         <v>16</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.07</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="16">
@@ -877,13 +877,13 @@
         <v>16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>-0.38</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="17">
@@ -900,13 +900,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="18">
@@ -923,13 +923,13 @@
         <v>28</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>-0.22</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="19">
@@ -946,7 +946,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>-0.36</v>
@@ -998,7 +998,7 @@
         <v>-0.26</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="22">
@@ -1038,13 +1038,13 @@
         <v>10</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>0.41</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="24">
@@ -1061,13 +1061,13 @@
         <v>16</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="25">
@@ -1084,7 +1084,7 @@
         <v>16</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>-0.06</v>
@@ -1130,13 +1130,13 @@
         <v>16</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="28">
@@ -1153,13 +1153,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="29">
@@ -1176,10 +1176,10 @@
         <v>16</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0.05</v>
@@ -1202,10 +1202,10 @@
         <v>0.2</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="31">
@@ -1245,13 +1245,13 @@
         <v>16</v>
       </c>
       <c r="E32" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>0.03</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0.04</v>
       </c>
     </row>
     <row r="33">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_o_higgins.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:42</t>
+    <t xml:space="preserve">2026-10-01 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_o_higgins.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:17</t>
+    <t xml:space="preserve">2026-10-05 19:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
